--- a/analysis_report.xlsx
+++ b/analysis_report.xlsx
@@ -747,7 +747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,148 +763,134 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>inputflow</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>resultflow</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>process_all</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>to_process</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>from_process</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>process_all</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>resultflow</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>to_process</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>transport_all</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>to_transport</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>from_transport</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>to_transport</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>transport</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>transport_all</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>inputflow</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>storage</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>65</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G2" t="n">
-        <v>65</v>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>65</v>
-      </c>
-      <c r="I3" t="n">
-        <v>65</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.25</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>65</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65</v>
+      </c>
+      <c r="I4" t="n">
+        <v>65</v>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>380</v>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>34</v>
@@ -916,25 +902,30 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L5" t="n">
+        <v>65</v>
+      </c>
       <c r="M5" t="n">
         <v>65</v>
       </c>
-      <c r="N5" t="n">
-        <v>65</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>380</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -942,21 +933,20 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>3542</v>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -966,9 +956,6 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>65</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -978,7 +965,9 @@
         <v>3</v>
       </c>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>257</v>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -986,21 +975,20 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
-        <v>257</v>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>3765</v>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -1008,21 +996,20 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
-        <v>3542</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>480</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
@@ -1030,21 +1017,20 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>3765</v>
-      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>920</v>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
@@ -1052,21 +1038,20 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>480</v>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>490</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -1074,21 +1059,20 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
-        <v>920</v>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>965</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -1096,33 +1080,8 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>490</v>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>965</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
